--- a/Teletrabajo/Teletrabajo.xlsx
+++ b/Teletrabajo/Teletrabajo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Maria Alejandra\Downloads\Pagina Web de Riesgo VS\Teletrabajo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9339B168-73D1-445A-A482-1C5ACC0C2AFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BCD256D-733D-43D1-8F4C-E4456AFB0417}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{DD785F99-1408-4CF3-B821-6417BD60C94A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DD785F99-1408-4CF3-B821-6417BD60C94A}"/>
   </bookViews>
   <sheets>
     <sheet name="Teletrabajo" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="33">
   <si>
     <t>Josue</t>
   </si>
@@ -135,6 +135,9 @@
   </si>
   <si>
     <t>Turno Madrugada</t>
+  </si>
+  <si>
+    <t>Semana del 25 - 29  de Mayo</t>
   </si>
 </sst>
 </file>
@@ -252,7 +255,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -271,6 +274,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -606,25 +610,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28B5EDDC-5ADB-4A4C-9736-3AC62D35C32F}">
   <dimension ref="A1:Q25"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="18.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="18.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.44140625" customWidth="1"/>
-    <col min="4" max="4" width="18.6640625" customWidth="1"/>
-    <col min="5" max="5" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="4.88671875" customWidth="1"/>
-    <col min="8" max="8" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="4.5546875" customWidth="1"/>
-    <col min="11" max="11" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="3.88671875" customWidth="1"/>
-    <col min="14" max="14" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="3.6640625" customWidth="1"/>
-    <col min="17" max="17" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="3.6640625" customWidth="1"/>
+    <col min="3" max="3" width="4.42578125" customWidth="1"/>
+    <col min="4" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="5" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.85546875" customWidth="1"/>
+    <col min="8" max="8" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="4.5703125" customWidth="1"/>
+    <col min="11" max="11" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="3.85546875" customWidth="1"/>
+    <col min="14" max="14" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="3.7109375" customWidth="1"/>
+    <col min="17" max="17" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="3.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>18</v>
       </c>
@@ -650,7 +654,7 @@
       </c>
       <c r="Q1" s="7"/>
     </row>
-    <row r="2" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>24</v>
       </c>
@@ -688,7 +692,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>16</v>
       </c>
@@ -726,7 +730,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
@@ -764,7 +768,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>10</v>
       </c>
@@ -802,7 +806,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>13</v>
       </c>
@@ -840,7 +844,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>14</v>
       </c>
@@ -878,7 +882,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>15</v>
       </c>
@@ -916,7 +920,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="D9" s="1" t="s">
         <v>5</v>
       </c>
@@ -948,7 +952,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="G10" s="1" t="s">
         <v>13</v>
       </c>
@@ -974,7 +978,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="J11" s="1" t="s">
         <v>13</v>
       </c>
@@ -994,7 +998,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="J12" s="1" t="s">
         <v>14</v>
       </c>
@@ -1014,7 +1018,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
         <v>17</v>
       </c>
@@ -1027,8 +1031,12 @@
         <v>30</v>
       </c>
       <c r="H14" s="7"/>
-    </row>
-    <row r="15" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="J14" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="K14" s="7"/>
+    </row>
+    <row r="15" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
         <v>24</v>
       </c>
@@ -1047,8 +1055,14 @@
       <c r="H15" s="2" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="16" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="J15" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="K15" s="8" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>16</v>
       </c>
@@ -1067,8 +1081,14 @@
       <c r="H16" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="17" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="J16" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K16" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>15</v>
       </c>
@@ -1087,8 +1107,14 @@
       <c r="H17" s="2" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="J17" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K17" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>5</v>
       </c>
@@ -1107,8 +1133,14 @@
       <c r="H18" s="2" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="19" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="J18" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="K18" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1127,8 +1159,14 @@
       <c r="H19" s="2" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="20" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="J19" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="K19" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>10</v>
       </c>
@@ -1147,8 +1185,14 @@
       <c r="H20" s="2" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="21" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="J20" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="K20" s="8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>12</v>
       </c>
@@ -1167,8 +1211,14 @@
       <c r="H21" s="2" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="22" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="J21" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="K21" s="8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>3</v>
       </c>
@@ -1181,8 +1231,14 @@
       <c r="E22" s="2" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="23" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="J22" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="K22" s="8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>0</v>
       </c>
@@ -1195,8 +1251,14 @@
       <c r="E23" s="2" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="24" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="J23" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="K23" s="8" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>13</v>
       </c>
@@ -1204,7 +1266,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>2</v>
       </c>
@@ -1213,7 +1275,7 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="10">
     <mergeCell ref="M1:N1"/>
     <mergeCell ref="P1:Q1"/>
     <mergeCell ref="D14:E14"/>
@@ -1223,6 +1285,7 @@
     <mergeCell ref="G1:H1"/>
     <mergeCell ref="J1:K1"/>
     <mergeCell ref="G14:H14"/>
+    <mergeCell ref="J14:K14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Teletrabajo/Teletrabajo.xlsx
+++ b/Teletrabajo/Teletrabajo.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Maria Alejandra\Downloads\Pagina Web de Riesgo VS\Teletrabajo\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://virtualsoftserv-my.sharepoint.com/personal/maria_sanchez_virtualsoft_tech/Documents/Indicadores y Pagina WEB/Teletrabajo/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BCD256D-733D-43D1-8F4C-E4456AFB0417}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{2BCD256D-733D-43D1-8F4C-E4456AFB0417}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6877372C-0CE7-472A-AFA7-4009EA21687F}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DD785F99-1408-4CF3-B821-6417BD60C94A}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="34">
   <si>
     <t>Josue</t>
   </si>
@@ -138,6 +138,9 @@
   </si>
   <si>
     <t>Semana del 25 - 29  de Mayo</t>
+  </si>
+  <si>
+    <t>Semana del 1 - 5  de Junio</t>
   </si>
 </sst>
 </file>
@@ -268,13 +271,13 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -629,30 +632,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="D1" s="6" t="s">
+      <c r="B1" s="8"/>
+      <c r="D1" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="E1" s="7"/>
-      <c r="G1" s="6" t="s">
+      <c r="E1" s="8"/>
+      <c r="G1" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="H1" s="7"/>
-      <c r="J1" s="6" t="s">
+      <c r="H1" s="8"/>
+      <c r="J1" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="K1" s="7"/>
-      <c r="M1" s="6" t="s">
+      <c r="K1" s="8"/>
+      <c r="M1" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="N1" s="7"/>
-      <c r="P1" s="6" t="s">
+      <c r="N1" s="8"/>
+      <c r="P1" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="Q1" s="7"/>
+      <c r="Q1" s="8"/>
     </row>
     <row r="2" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
@@ -1019,22 +1022,26 @@
       </c>
     </row>
     <row r="14" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A14" s="6" t="s">
+      <c r="A14" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="7"/>
-      <c r="D14" s="6" t="s">
+      <c r="B14" s="8"/>
+      <c r="D14" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="E14" s="7"/>
-      <c r="G14" s="6" t="s">
+      <c r="E14" s="8"/>
+      <c r="G14" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="H14" s="7"/>
-      <c r="J14" s="6" t="s">
+      <c r="H14" s="8"/>
+      <c r="J14" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="K14" s="7"/>
+      <c r="K14" s="8"/>
+      <c r="M14" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="N14" s="8"/>
     </row>
     <row r="15" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
@@ -1058,8 +1065,14 @@
       <c r="J15" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="K15" s="8" t="s">
+      <c r="K15" s="6" t="s">
         <v>1</v>
+      </c>
+      <c r="M15" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="N15" s="6" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
@@ -1084,11 +1097,17 @@
       <c r="J16" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="K16" s="8" t="s">
+      <c r="K16" s="6" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="17" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="M16" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="N16" s="6" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>15</v>
       </c>
@@ -1110,11 +1129,17 @@
       <c r="J17" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="K17" s="8" t="s">
+      <c r="K17" s="6" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="18" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="M17" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="N17" s="6" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>5</v>
       </c>
@@ -1136,11 +1161,17 @@
       <c r="J18" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="K18" s="8" t="s">
+      <c r="K18" s="6" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="19" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="M18" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N18" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1162,11 +1193,17 @@
       <c r="J19" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="K19" s="8" t="s">
+      <c r="K19" s="6" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="20" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="M19" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="N19" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>10</v>
       </c>
@@ -1188,11 +1225,17 @@
       <c r="J20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="K20" s="8" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="K20" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="M20" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="N20" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>12</v>
       </c>
@@ -1214,11 +1257,17 @@
       <c r="J21" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="K21" s="8" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="K21" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="M21" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="N21" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>3</v>
       </c>
@@ -1234,11 +1283,17 @@
       <c r="J22" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="K22" s="8" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="K22" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="M22" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="N22" s="6" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>0</v>
       </c>
@@ -1254,11 +1309,11 @@
       <c r="J23" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="K23" s="8" t="s">
+      <c r="K23" s="6" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="24" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>13</v>
       </c>
@@ -1266,7 +1321,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="25" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>2</v>
       </c>
@@ -1275,7 +1330,7 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="M1:N1"/>
     <mergeCell ref="P1:Q1"/>
     <mergeCell ref="D14:E14"/>
@@ -1286,6 +1341,7 @@
     <mergeCell ref="J1:K1"/>
     <mergeCell ref="G14:H14"/>
     <mergeCell ref="J14:K14"/>
+    <mergeCell ref="M14:N14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Teletrabajo/Teletrabajo.xlsx
+++ b/Teletrabajo/Teletrabajo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://virtualsoftserv-my.sharepoint.com/personal/maria_sanchez_virtualsoft_tech/Documents/Indicadores y Pagina WEB/Teletrabajo/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{2BCD256D-733D-43D1-8F4C-E4456AFB0417}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6877372C-0CE7-472A-AFA7-4009EA21687F}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{2BCD256D-733D-43D1-8F4C-E4456AFB0417}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EFDE3343-B6A1-4EAA-B152-95F8A5A24219}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DD785F99-1408-4CF3-B821-6417BD60C94A}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{DD785F99-1408-4CF3-B821-6417BD60C94A}"/>
   </bookViews>
   <sheets>
     <sheet name="Teletrabajo" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="36">
   <si>
     <t>Josue</t>
   </si>
@@ -141,13 +141,19 @@
   </si>
   <si>
     <t>Semana del 1 - 5  de Junio</t>
+  </si>
+  <si>
+    <t>Semana del 8 - 10 de Junio</t>
+  </si>
+  <si>
+    <t>Miecoles</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -168,6 +174,12 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="5">
@@ -258,7 +270,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -277,6 +289,12 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -612,26 +630,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28B5EDDC-5ADB-4A4C-9736-3AC62D35C32F}">
-  <dimension ref="A1:Q25"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="18.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:Q36"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="18.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.5546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.42578125" customWidth="1"/>
-    <col min="4" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="5" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="4.85546875" customWidth="1"/>
-    <col min="8" max="8" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="4.5703125" customWidth="1"/>
-    <col min="11" max="11" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="3.85546875" customWidth="1"/>
-    <col min="14" max="14" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="3.7109375" customWidth="1"/>
-    <col min="17" max="17" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="3.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.44140625" customWidth="1"/>
+    <col min="4" max="4" width="18.6640625" customWidth="1"/>
+    <col min="5" max="5" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.88671875" customWidth="1"/>
+    <col min="8" max="8" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="4.5546875" customWidth="1"/>
+    <col min="11" max="11" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="3.88671875" customWidth="1"/>
+    <col min="14" max="14" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="3.6640625" customWidth="1"/>
+    <col min="17" max="17" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="3.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
         <v>18</v>
       </c>
@@ -657,7 +675,7 @@
       </c>
       <c r="Q1" s="8"/>
     </row>
-    <row r="2" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>24</v>
       </c>
@@ -695,7 +713,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>16</v>
       </c>
@@ -733,7 +751,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
@@ -771,7 +789,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>10</v>
       </c>
@@ -809,7 +827,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>13</v>
       </c>
@@ -847,7 +865,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>14</v>
       </c>
@@ -885,7 +903,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>15</v>
       </c>
@@ -923,7 +941,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
       <c r="D9" s="1" t="s">
         <v>5</v>
       </c>
@@ -955,7 +973,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
       <c r="G10" s="1" t="s">
         <v>13</v>
       </c>
@@ -981,7 +999,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
       <c r="J11" s="1" t="s">
         <v>13</v>
       </c>
@@ -1001,7 +1019,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
       <c r="J12" s="1" t="s">
         <v>14</v>
       </c>
@@ -1021,7 +1039,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A14" s="7" t="s">
         <v>17</v>
       </c>
@@ -1043,7 +1061,7 @@
       </c>
       <c r="N14" s="8"/>
     </row>
-    <row r="15" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
         <v>24</v>
       </c>
@@ -1075,7 +1093,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>16</v>
       </c>
@@ -1107,7 +1125,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>15</v>
       </c>
@@ -1139,7 +1157,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>5</v>
       </c>
@@ -1171,7 +1189,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1203,7 +1221,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="20" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>10</v>
       </c>
@@ -1235,7 +1253,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="21" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>12</v>
       </c>
@@ -1267,7 +1285,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="22" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>3</v>
       </c>
@@ -1293,7 +1311,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="23" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>0</v>
       </c>
@@ -1313,7 +1331,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="24" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>13</v>
       </c>
@@ -1321,7 +1339,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="25" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>2</v>
       </c>
@@ -1329,8 +1347,79 @@
         <v>26</v>
       </c>
     </row>
+    <row r="28" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A28" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="B28" s="9"/>
+    </row>
+    <row r="29" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A29" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A30" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A31" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A32" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A33" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A34" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A35" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A36" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="12">
+    <mergeCell ref="A28:B28"/>
     <mergeCell ref="M1:N1"/>
     <mergeCell ref="P1:Q1"/>
     <mergeCell ref="D14:E14"/>

--- a/Teletrabajo/Teletrabajo.xlsx
+++ b/Teletrabajo/Teletrabajo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://virtualsoftserv-my.sharepoint.com/personal/maria_sanchez_virtualsoft_tech/Documents/Indicadores y Pagina WEB/Teletrabajo/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{2BCD256D-733D-43D1-8F4C-E4456AFB0417}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EFDE3343-B6A1-4EAA-B152-95F8A5A24219}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{2BCD256D-733D-43D1-8F4C-E4456AFB0417}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5679F156-F030-402E-B53D-FD49DA3732CF}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{DD785F99-1408-4CF3-B821-6417BD60C94A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DD785F99-1408-4CF3-B821-6417BD60C94A}"/>
   </bookViews>
   <sheets>
     <sheet name="Teletrabajo" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="36">
   <si>
     <t>Josue</t>
   </si>
@@ -284,17 +284,17 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -630,52 +630,52 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28B5EDDC-5ADB-4A4C-9736-3AC62D35C32F}">
-  <dimension ref="A1:Q36"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="18.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:Q33"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="18.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.44140625" customWidth="1"/>
-    <col min="4" max="4" width="18.6640625" customWidth="1"/>
-    <col min="5" max="5" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="4.88671875" customWidth="1"/>
-    <col min="8" max="8" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="4.5546875" customWidth="1"/>
-    <col min="11" max="11" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="3.88671875" customWidth="1"/>
-    <col min="14" max="14" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="3.6640625" customWidth="1"/>
-    <col min="17" max="17" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="3.6640625" customWidth="1"/>
+    <col min="3" max="3" width="4.42578125" customWidth="1"/>
+    <col min="4" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="5" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.85546875" customWidth="1"/>
+    <col min="8" max="8" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="4.5703125" customWidth="1"/>
+    <col min="11" max="11" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="3.85546875" customWidth="1"/>
+    <col min="14" max="14" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="3.7109375" customWidth="1"/>
+    <col min="17" max="17" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="3.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="7" t="s">
+    <row r="1" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="D1" s="7" t="s">
+      <c r="B1" s="10"/>
+      <c r="D1" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="E1" s="8"/>
-      <c r="G1" s="7" t="s">
+      <c r="E1" s="10"/>
+      <c r="G1" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="H1" s="8"/>
-      <c r="J1" s="7" t="s">
+      <c r="H1" s="10"/>
+      <c r="J1" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="K1" s="8"/>
-      <c r="M1" s="7" t="s">
+      <c r="K1" s="10"/>
+      <c r="M1" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="N1" s="8"/>
-      <c r="P1" s="7" t="s">
+      <c r="N1" s="10"/>
+      <c r="P1" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="Q1" s="8"/>
-    </row>
-    <row r="2" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q1" s="10"/>
+    </row>
+    <row r="2" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>24</v>
       </c>
@@ -713,7 +713,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>16</v>
       </c>
@@ -751,7 +751,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
@@ -789,7 +789,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>10</v>
       </c>
@@ -827,7 +827,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>13</v>
       </c>
@@ -865,7 +865,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>14</v>
       </c>
@@ -903,7 +903,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>15</v>
       </c>
@@ -941,7 +941,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="D9" s="1" t="s">
         <v>5</v>
       </c>
@@ -973,7 +973,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="G10" s="1" t="s">
         <v>13</v>
       </c>
@@ -999,7 +999,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="J11" s="1" t="s">
         <v>13</v>
       </c>
@@ -1019,7 +1019,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="J12" s="1" t="s">
         <v>14</v>
       </c>
@@ -1039,29 +1039,29 @@
         <v>26</v>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A14" s="7" t="s">
+    <row r="14" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A14" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="8"/>
-      <c r="D14" s="7" t="s">
+      <c r="B14" s="10"/>
+      <c r="D14" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="E14" s="8"/>
-      <c r="G14" s="7" t="s">
+      <c r="E14" s="10"/>
+      <c r="G14" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="H14" s="8"/>
-      <c r="J14" s="7" t="s">
+      <c r="H14" s="10"/>
+      <c r="J14" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="K14" s="8"/>
-      <c r="M14" s="7" t="s">
+      <c r="K14" s="10"/>
+      <c r="M14" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="N14" s="8"/>
-    </row>
-    <row r="15" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="N14" s="10"/>
+    </row>
+    <row r="15" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
         <v>24</v>
       </c>
@@ -1093,7 +1093,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>16</v>
       </c>
@@ -1125,7 +1125,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>15</v>
       </c>
@@ -1157,7 +1157,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>5</v>
       </c>
@@ -1189,7 +1189,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1221,7 +1221,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="20" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>10</v>
       </c>
@@ -1253,7 +1253,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="21" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>12</v>
       </c>
@@ -1285,7 +1285,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="22" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>3</v>
       </c>
@@ -1311,7 +1311,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="23" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>0</v>
       </c>
@@ -1331,7 +1331,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="24" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>13</v>
       </c>
@@ -1339,7 +1339,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="25" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>2</v>
       </c>
@@ -1347,73 +1347,49 @@
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A28" s="9" t="s">
+    <row r="28" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A28" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B28" s="9"/>
-    </row>
-    <row r="29" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A29" s="10" t="s">
+      <c r="B28" s="8"/>
+    </row>
+    <row r="29" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A29" s="7" t="s">
         <v>5</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="30" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A30" s="10" t="s">
+    <row r="30" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A30" s="7" t="s">
         <v>3</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="31" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A31" s="10" t="s">
+    <row r="31" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A31" s="7" t="s">
         <v>13</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="32" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A32" s="10" t="s">
+    <row r="32" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A32" s="7" t="s">
         <v>16</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="33" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A33" s="10" t="s">
-        <v>15</v>
+    <row r="33" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A33" s="7" t="s">
+        <v>2</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A34" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A35" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A36" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="B36" s="2" t="s">
         <v>31</v>
       </c>
     </row>

--- a/Teletrabajo/Teletrabajo.xlsx
+++ b/Teletrabajo/Teletrabajo.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://virtualsoftserv-my.sharepoint.com/personal/maria_sanchez_virtualsoft_tech/Documents/Indicadores y Pagina WEB/Teletrabajo/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{2BCD256D-733D-43D1-8F4C-E4456AFB0417}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5679F156-F030-402E-B53D-FD49DA3732CF}"/>
+  <xr:revisionPtr revIDLastSave="15" documentId="13_ncr:1_{2BCD256D-733D-43D1-8F4C-E4456AFB0417}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DD344004-E672-4E4D-973E-F89CC4129A16}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DD785F99-1408-4CF3-B821-6417BD60C94A}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{DD785F99-1408-4CF3-B821-6417BD60C94A}"/>
   </bookViews>
   <sheets>
     <sheet name="Teletrabajo" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="37">
   <si>
     <t>Josue</t>
   </si>
@@ -147,6 +147,9 @@
   </si>
   <si>
     <t>Miecoles</t>
+  </si>
+  <si>
+    <t>Semana del 21 - 24 de Julio</t>
   </si>
 </sst>
 </file>
@@ -631,25 +634,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28B5EDDC-5ADB-4A4C-9736-3AC62D35C32F}">
   <dimension ref="A1:Q33"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="18.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="18.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.5546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.42578125" customWidth="1"/>
-    <col min="4" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="5" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="4.85546875" customWidth="1"/>
-    <col min="8" max="8" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="4.5703125" customWidth="1"/>
-    <col min="11" max="11" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="3.85546875" customWidth="1"/>
-    <col min="14" max="14" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="3.7109375" customWidth="1"/>
-    <col min="17" max="17" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="3.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.44140625" customWidth="1"/>
+    <col min="4" max="4" width="18.6640625" customWidth="1"/>
+    <col min="5" max="5" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.88671875" customWidth="1"/>
+    <col min="8" max="8" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="4.5546875" customWidth="1"/>
+    <col min="11" max="11" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="3.88671875" customWidth="1"/>
+    <col min="14" max="14" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="3.6640625" customWidth="1"/>
+    <col min="17" max="17" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="3.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="9" t="s">
         <v>18</v>
       </c>
@@ -675,7 +678,7 @@
       </c>
       <c r="Q1" s="10"/>
     </row>
-    <row r="2" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>24</v>
       </c>
@@ -713,7 +716,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>16</v>
       </c>
@@ -751,7 +754,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
@@ -789,7 +792,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>10</v>
       </c>
@@ -827,7 +830,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>13</v>
       </c>
@@ -865,7 +868,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>14</v>
       </c>
@@ -903,7 +906,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>15</v>
       </c>
@@ -941,7 +944,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
       <c r="D9" s="1" t="s">
         <v>5</v>
       </c>
@@ -973,7 +976,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
       <c r="G10" s="1" t="s">
         <v>13</v>
       </c>
@@ -999,7 +1002,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
       <c r="J11" s="1" t="s">
         <v>13</v>
       </c>
@@ -1019,7 +1022,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
       <c r="J12" s="1" t="s">
         <v>14</v>
       </c>
@@ -1039,7 +1042,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A14" s="9" t="s">
         <v>17</v>
       </c>
@@ -1061,7 +1064,7 @@
       </c>
       <c r="N14" s="10"/>
     </row>
-    <row r="15" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
         <v>24</v>
       </c>
@@ -1093,7 +1096,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>16</v>
       </c>
@@ -1125,7 +1128,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>15</v>
       </c>
@@ -1157,7 +1160,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>5</v>
       </c>
@@ -1189,7 +1192,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1221,7 +1224,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="20" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>10</v>
       </c>
@@ -1253,7 +1256,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="21" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>12</v>
       </c>
@@ -1285,7 +1288,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="22" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>3</v>
       </c>
@@ -1311,7 +1314,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="23" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>0</v>
       </c>
@@ -1331,7 +1334,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="24" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>13</v>
       </c>
@@ -1339,7 +1342,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="25" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>2</v>
       </c>
@@ -1347,37 +1350,59 @@
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A28" s="8" t="s">
         <v>34</v>
       </c>
       <c r="B28" s="8"/>
-    </row>
-    <row r="29" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D28" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="E28" s="8"/>
+    </row>
+    <row r="29" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A29" s="7" t="s">
         <v>5</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D29" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A30" s="7" t="s">
         <v>3</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="31" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D30" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A31" s="7" t="s">
         <v>13</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="32" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D31" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A32" s="7" t="s">
         <v>16</v>
       </c>
@@ -1385,7 +1410,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="33" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A33" s="7" t="s">
         <v>2</v>
       </c>
@@ -1394,7 +1419,7 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="13">
     <mergeCell ref="A28:B28"/>
     <mergeCell ref="M1:N1"/>
     <mergeCell ref="P1:Q1"/>
@@ -1407,6 +1432,7 @@
     <mergeCell ref="G14:H14"/>
     <mergeCell ref="J14:K14"/>
     <mergeCell ref="M14:N14"/>
+    <mergeCell ref="D28:E28"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Teletrabajo/Teletrabajo.xlsx
+++ b/Teletrabajo/Teletrabajo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://virtualsoftserv-my.sharepoint.com/personal/maria_sanchez_virtualsoft_tech/Documents/Indicadores y Pagina WEB/Teletrabajo/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="15" documentId="13_ncr:1_{2BCD256D-733D-43D1-8F4C-E4456AFB0417}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DD344004-E672-4E4D-973E-F89CC4129A16}"/>
+  <xr:revisionPtr revIDLastSave="16" documentId="13_ncr:1_{2BCD256D-733D-43D1-8F4C-E4456AFB0417}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A18DD47B-BA3C-4AF2-9299-2EA07C47029C}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{DD785F99-1408-4CF3-B821-6417BD60C94A}"/>
+    <workbookView xWindow="3510" yWindow="3510" windowWidth="21600" windowHeight="11295" xr2:uid="{DD785F99-1408-4CF3-B821-6417BD60C94A}"/>
   </bookViews>
   <sheets>
     <sheet name="Teletrabajo" sheetId="1" r:id="rId1"/>
@@ -634,25 +634,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28B5EDDC-5ADB-4A4C-9736-3AC62D35C32F}">
   <dimension ref="A1:Q33"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="18.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="18.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.44140625" customWidth="1"/>
-    <col min="4" max="4" width="18.6640625" customWidth="1"/>
-    <col min="5" max="5" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="4.88671875" customWidth="1"/>
-    <col min="8" max="8" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="4.5546875" customWidth="1"/>
-    <col min="11" max="11" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="3.88671875" customWidth="1"/>
-    <col min="14" max="14" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="3.6640625" customWidth="1"/>
-    <col min="17" max="17" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="3.6640625" customWidth="1"/>
+    <col min="3" max="3" width="4.42578125" customWidth="1"/>
+    <col min="4" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="5" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.85546875" customWidth="1"/>
+    <col min="8" max="8" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="4.5703125" customWidth="1"/>
+    <col min="11" max="11" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="3.85546875" customWidth="1"/>
+    <col min="14" max="14" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="3.7109375" customWidth="1"/>
+    <col min="17" max="17" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="3.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
         <v>18</v>
       </c>
@@ -678,7 +678,7 @@
       </c>
       <c r="Q1" s="10"/>
     </row>
-    <row r="2" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>24</v>
       </c>
@@ -716,7 +716,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>16</v>
       </c>
@@ -754,7 +754,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
@@ -792,7 +792,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>10</v>
       </c>
@@ -830,7 +830,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>13</v>
       </c>
@@ -868,7 +868,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>14</v>
       </c>
@@ -906,7 +906,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>15</v>
       </c>
@@ -944,7 +944,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="D9" s="1" t="s">
         <v>5</v>
       </c>
@@ -976,7 +976,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="G10" s="1" t="s">
         <v>13</v>
       </c>
@@ -1002,7 +1002,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="J11" s="1" t="s">
         <v>13</v>
       </c>
@@ -1022,7 +1022,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="J12" s="1" t="s">
         <v>14</v>
       </c>
@@ -1042,7 +1042,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" s="9" t="s">
         <v>17</v>
       </c>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="N14" s="10"/>
     </row>
-    <row r="15" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
         <v>24</v>
       </c>
@@ -1096,7 +1096,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>16</v>
       </c>
@@ -1128,7 +1128,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>15</v>
       </c>
@@ -1160,7 +1160,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>5</v>
       </c>
@@ -1192,7 +1192,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1224,7 +1224,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="20" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>10</v>
       </c>
@@ -1256,7 +1256,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="21" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>12</v>
       </c>
@@ -1288,7 +1288,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="22" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>3</v>
       </c>
@@ -1314,7 +1314,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="23" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>0</v>
       </c>
@@ -1334,7 +1334,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="24" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>13</v>
       </c>
@@ -1342,7 +1342,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="25" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>2</v>
       </c>
@@ -1350,7 +1350,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28" s="8" t="s">
         <v>34</v>
       </c>
@@ -1360,7 +1360,7 @@
       </c>
       <c r="E28" s="8"/>
     </row>
-    <row r="29" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
         <v>5</v>
       </c>
@@ -1374,7 +1374,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="30" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" s="7" t="s">
         <v>3</v>
       </c>
@@ -1388,7 +1388,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="31" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
         <v>13</v>
       </c>
@@ -1396,13 +1396,13 @@
         <v>35</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="32" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" s="7" t="s">
         <v>16</v>
       </c>
@@ -1410,7 +1410,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="33" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
         <v>2</v>
       </c>

--- a/Teletrabajo/Teletrabajo.xlsx
+++ b/Teletrabajo/Teletrabajo.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://virtualsoftserv-my.sharepoint.com/personal/maria_sanchez_virtualsoft_tech/Documents/Indicadores y Pagina WEB/Teletrabajo/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="41" documentId="13_ncr:1_{2BCD256D-733D-43D1-8F4C-E4456AFB0417}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{85B7109F-7A98-44D2-B78C-AE6A9628C080}"/>
+  <xr:revisionPtr revIDLastSave="48" documentId="13_ncr:1_{2BCD256D-733D-43D1-8F4C-E4456AFB0417}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C433DC3F-73FB-4639-96A7-86B318010383}"/>
   <bookViews>
-    <workbookView xWindow="2550" yWindow="1590" windowWidth="21600" windowHeight="11295" xr2:uid="{DD785F99-1408-4CF3-B821-6417BD60C94A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DD785F99-1408-4CF3-B821-6417BD60C94A}"/>
   </bookViews>
   <sheets>
     <sheet name="Teletrabajo" sheetId="1" r:id="rId1"/>
@@ -192,6 +192,7 @@
       <sz val="12"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="5">

--- a/Teletrabajo/Teletrabajo.xlsx
+++ b/Teletrabajo/Teletrabajo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://virtualsoftserv-my.sharepoint.com/personal/maria_sanchez_virtualsoft_tech/Documents/Indicadores y Pagina WEB/Teletrabajo/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="48" documentId="13_ncr:1_{2BCD256D-733D-43D1-8F4C-E4456AFB0417}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C433DC3F-73FB-4639-96A7-86B318010383}"/>
+  <xr:revisionPtr revIDLastSave="70" documentId="13_ncr:1_{2BCD256D-733D-43D1-8F4C-E4456AFB0417}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F3471194-D1CC-4E32-9D95-A59E5E4E66C3}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DD785F99-1408-4CF3-B821-6417BD60C94A}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="42">
   <si>
     <t>Josue</t>
   </si>
@@ -159,6 +159,12 @@
   </si>
   <si>
     <t xml:space="preserve">Lunes </t>
+  </si>
+  <si>
+    <t>Semana del 3 al 7 Agosto</t>
+  </si>
+  <si>
+    <t>Semana del 10 al 14 Agosto</t>
   </si>
 </sst>
 </file>
@@ -1374,6 +1380,14 @@
         <v>32</v>
       </c>
       <c r="H28" s="8"/>
+      <c r="J28" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="K28" s="8"/>
+      <c r="M28" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="N28" s="8"/>
     </row>
     <row r="29" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
@@ -1394,6 +1408,18 @@
       <c r="H29" s="2" t="s">
         <v>39</v>
       </c>
+      <c r="J29" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="K29" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="M29" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="N29" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="30" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" s="7" t="s">
@@ -1414,6 +1440,18 @@
       <c r="H30" s="2" t="s">
         <v>4</v>
       </c>
+      <c r="J30" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="K30" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M30" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="N30" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="31" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
@@ -1434,6 +1472,18 @@
       <c r="H31" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="J31" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="K31" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M31" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="N31" s="2" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="32" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" s="7" t="s">
@@ -1464,7 +1514,7 @@
       <c r="H34" s="2"/>
     </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="16">
     <mergeCell ref="A28:B28"/>
     <mergeCell ref="M1:N1"/>
     <mergeCell ref="P1:Q1"/>
@@ -1479,6 +1529,8 @@
     <mergeCell ref="M14:N14"/>
     <mergeCell ref="D28:E28"/>
     <mergeCell ref="G28:H28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="M28:N28"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Teletrabajo/Teletrabajo.xlsx
+++ b/Teletrabajo/Teletrabajo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://virtualsoftserv-my.sharepoint.com/personal/maria_sanchez_virtualsoft_tech/Documents/Indicadores y Pagina WEB/Teletrabajo/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="70" documentId="13_ncr:1_{2BCD256D-733D-43D1-8F4C-E4456AFB0417}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F3471194-D1CC-4E32-9D95-A59E5E4E66C3}"/>
+  <xr:revisionPtr revIDLastSave="75" documentId="13_ncr:1_{2BCD256D-733D-43D1-8F4C-E4456AFB0417}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C2BE4490-82FA-4A56-BD07-37916A3D62BB}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DD785F99-1408-4CF3-B821-6417BD60C94A}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="43">
   <si>
     <t>Josue</t>
   </si>
@@ -165,6 +165,9 @@
   </si>
   <si>
     <t>Semana del 10 al 14 Agosto</t>
+  </si>
+  <si>
+    <t>Semana del 17 al 21 Agosto</t>
   </si>
 </sst>
 </file>
@@ -649,7 +652,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28B5EDDC-5ADB-4A4C-9736-3AC62D35C32F}">
-  <dimension ref="A1:Q34"/>
+  <dimension ref="A1:Q39"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="18.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.5703125" bestFit="1" customWidth="1"/>
@@ -1513,8 +1516,35 @@
       <c r="G34" s="1"/>
       <c r="H34" s="2"/>
     </row>
+    <row r="36" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A36" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="B36" s="8"/>
+    </row>
+    <row r="37" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A39" s="1"/>
+      <c r="B39" s="2"/>
+    </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="17">
+    <mergeCell ref="A36:B36"/>
     <mergeCell ref="A28:B28"/>
     <mergeCell ref="M1:N1"/>
     <mergeCell ref="P1:Q1"/>

--- a/Teletrabajo/Teletrabajo.xlsx
+++ b/Teletrabajo/Teletrabajo.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="75" documentId="13_ncr:1_{2BCD256D-733D-43D1-8F4C-E4456AFB0417}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C2BE4490-82FA-4A56-BD07-37916A3D62BB}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DD785F99-1408-4CF3-B821-6417BD60C94A}"/>
+    <workbookView xWindow="28680" yWindow="5280" windowWidth="23280" windowHeight="12480" xr2:uid="{DD785F99-1408-4CF3-B821-6417BD60C94A}"/>
   </bookViews>
   <sheets>
     <sheet name="Teletrabajo" sheetId="1" r:id="rId1"/>
@@ -309,10 +309,10 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -673,27 +673,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>18</v>
       </c>
       <c r="B1" s="10"/>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="8" t="s">
         <v>19</v>
       </c>
       <c r="E1" s="10"/>
-      <c r="G1" s="9" t="s">
+      <c r="G1" s="8" t="s">
         <v>20</v>
       </c>
       <c r="H1" s="10"/>
-      <c r="J1" s="9" t="s">
+      <c r="J1" s="8" t="s">
         <v>21</v>
       </c>
       <c r="K1" s="10"/>
-      <c r="M1" s="9" t="s">
+      <c r="M1" s="8" t="s">
         <v>22</v>
       </c>
       <c r="N1" s="10"/>
-      <c r="P1" s="9" t="s">
+      <c r="P1" s="8" t="s">
         <v>23</v>
       </c>
       <c r="Q1" s="10"/>
@@ -1063,23 +1063,23 @@
       </c>
     </row>
     <row r="14" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A14" s="9" t="s">
+      <c r="A14" s="8" t="s">
         <v>17</v>
       </c>
       <c r="B14" s="10"/>
-      <c r="D14" s="9" t="s">
+      <c r="D14" s="8" t="s">
         <v>29</v>
       </c>
       <c r="E14" s="10"/>
-      <c r="G14" s="9" t="s">
+      <c r="G14" s="8" t="s">
         <v>37</v>
       </c>
       <c r="H14" s="10"/>
-      <c r="J14" s="9" t="s">
+      <c r="J14" s="8" t="s">
         <v>35</v>
       </c>
       <c r="K14" s="10"/>
-      <c r="M14" s="9" t="s">
+      <c r="M14" s="8" t="s">
         <v>36</v>
       </c>
       <c r="N14" s="10"/>
@@ -1371,26 +1371,26 @@
       </c>
     </row>
     <row r="28" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A28" s="8" t="s">
+      <c r="A28" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="B28" s="8"/>
-      <c r="D28" s="8" t="s">
+      <c r="B28" s="9"/>
+      <c r="D28" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="E28" s="8"/>
-      <c r="G28" s="8" t="s">
+      <c r="E28" s="9"/>
+      <c r="G28" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="H28" s="8"/>
-      <c r="J28" s="9" t="s">
+      <c r="H28" s="9"/>
+      <c r="J28" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="K28" s="8"/>
-      <c r="M28" s="9" t="s">
+      <c r="K28" s="9"/>
+      <c r="M28" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="N28" s="8"/>
+      <c r="N28" s="9"/>
     </row>
     <row r="29" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
@@ -1517,10 +1517,10 @@
       <c r="H34" s="2"/>
     </row>
     <row r="36" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A36" s="9" t="s">
+      <c r="A36" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="B36" s="8"/>
+      <c r="B36" s="9"/>
     </row>
     <row r="37" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
@@ -1544,6 +1544,7 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="M28:N28"/>
     <mergeCell ref="A36:B36"/>
     <mergeCell ref="A28:B28"/>
     <mergeCell ref="M1:N1"/>
@@ -1560,7 +1561,6 @@
     <mergeCell ref="D28:E28"/>
     <mergeCell ref="G28:H28"/>
     <mergeCell ref="J28:K28"/>
-    <mergeCell ref="M28:N28"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Teletrabajo/Teletrabajo.xlsx
+++ b/Teletrabajo/Teletrabajo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://virtualsoftserv-my.sharepoint.com/personal/maria_sanchez_virtualsoft_tech/Documents/Indicadores y Pagina WEB/Teletrabajo/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="75" documentId="13_ncr:1_{2BCD256D-733D-43D1-8F4C-E4456AFB0417}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C2BE4490-82FA-4A56-BD07-37916A3D62BB}"/>
+  <xr:revisionPtr revIDLastSave="80" documentId="13_ncr:1_{2BCD256D-733D-43D1-8F4C-E4456AFB0417}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7CA5E9F9-7FD3-4F8A-A65A-79297BD1DF1A}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="5280" windowWidth="23280" windowHeight="12480" xr2:uid="{DD785F99-1408-4CF3-B821-6417BD60C94A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DD785F99-1408-4CF3-B821-6417BD60C94A}"/>
   </bookViews>
   <sheets>
     <sheet name="Teletrabajo" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="43">
   <si>
     <t>Josue</t>
   </si>
@@ -652,7 +652,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28B5EDDC-5ADB-4A4C-9736-3AC62D35C32F}">
-  <dimension ref="A1:Q39"/>
+  <dimension ref="A1:Q40"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="18.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.5703125" bestFit="1" customWidth="1"/>
@@ -1521,6 +1521,10 @@
         <v>42</v>
       </c>
       <c r="B36" s="9"/>
+      <c r="D36" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="E36" s="9"/>
     </row>
     <row r="37" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
@@ -1529,6 +1533,12 @@
       <c r="B37" s="2" t="s">
         <v>4</v>
       </c>
+      <c r="D37" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="38" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
@@ -1537,13 +1547,35 @@
       <c r="B38" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="D38" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="39" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39" s="1"/>
       <c r="B39" s="2"/>
+      <c r="D39" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D40" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>11</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="17">
+  <mergeCells count="18">
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="D36:E36"/>
     <mergeCell ref="M28:N28"/>
     <mergeCell ref="A36:B36"/>
     <mergeCell ref="A28:B28"/>
@@ -1560,7 +1592,6 @@
     <mergeCell ref="M14:N14"/>
     <mergeCell ref="D28:E28"/>
     <mergeCell ref="G28:H28"/>
-    <mergeCell ref="J28:K28"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Teletrabajo/Teletrabajo.xlsx
+++ b/Teletrabajo/Teletrabajo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://virtualsoftserv-my.sharepoint.com/personal/maria_sanchez_virtualsoft_tech/Documents/Indicadores y Pagina WEB/Teletrabajo/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="80" documentId="13_ncr:1_{2BCD256D-733D-43D1-8F4C-E4456AFB0417}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7CA5E9F9-7FD3-4F8A-A65A-79297BD1DF1A}"/>
+  <xr:revisionPtr revIDLastSave="81" documentId="13_ncr:1_{2BCD256D-733D-43D1-8F4C-E4456AFB0417}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FA8E7C56-5491-4CC6-8BC2-BC4230F75EF9}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DD785F99-1408-4CF3-B821-6417BD60C94A}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="44">
   <si>
     <t>Josue</t>
   </si>
@@ -168,6 +168,9 @@
   </si>
   <si>
     <t>Semana del 17 al 21 Agosto</t>
+  </si>
+  <si>
+    <t>Semana del 24 al 28 Agosto</t>
   </si>
 </sst>
 </file>
@@ -1522,7 +1525,7 @@
       </c>
       <c r="B36" s="9"/>
       <c r="D36" s="8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E36" s="9"/>
     </row>
@@ -1574,11 +1577,6 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="D36:E36"/>
-    <mergeCell ref="M28:N28"/>
-    <mergeCell ref="A36:B36"/>
-    <mergeCell ref="A28:B28"/>
     <mergeCell ref="M1:N1"/>
     <mergeCell ref="P1:Q1"/>
     <mergeCell ref="D14:E14"/>
@@ -1590,6 +1588,11 @@
     <mergeCell ref="G14:H14"/>
     <mergeCell ref="J14:K14"/>
     <mergeCell ref="M14:N14"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="D36:E36"/>
+    <mergeCell ref="M28:N28"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="A28:B28"/>
     <mergeCell ref="D28:E28"/>
     <mergeCell ref="G28:H28"/>
   </mergeCells>

--- a/Teletrabajo/Teletrabajo.xlsx
+++ b/Teletrabajo/Teletrabajo.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://virtualsoftserv-my.sharepoint.com/personal/maria_sanchez_virtualsoft_tech/Documents/Indicadores y Pagina WEB/Teletrabajo/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Daniel Puentes\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="81" documentId="13_ncr:1_{2BCD256D-733D-43D1-8F4C-E4456AFB0417}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FA8E7C56-5491-4CC6-8BC2-BC4230F75EF9}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A8D5AAD-EBDF-46B5-BE47-BA70C5B65919}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DD785F99-1408-4CF3-B821-6417BD60C94A}"/>
+    <workbookView xWindow="-25905" yWindow="4830" windowWidth="21600" windowHeight="11340" xr2:uid="{DD785F99-1408-4CF3-B821-6417BD60C94A}"/>
   </bookViews>
   <sheets>
     <sheet name="Teletrabajo" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="45">
   <si>
     <t>Josue</t>
   </si>
@@ -171,13 +171,16 @@
   </si>
   <si>
     <t>Semana del 24 al 28 Agosto</t>
+  </si>
+  <si>
+    <t>Semana del 31 Agosto al 4 de Septiembre</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -206,8 +209,15 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -230,6 +240,12 @@
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.14999847407452621"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9D9D9"/>
+        <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
   </fills>
@@ -295,7 +311,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -315,12 +331,13 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -679,27 +696,27 @@
       <c r="A1" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="10"/>
+      <c r="B1" s="9"/>
       <c r="D1" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="E1" s="10"/>
+      <c r="E1" s="9"/>
       <c r="G1" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="H1" s="10"/>
+      <c r="H1" s="9"/>
       <c r="J1" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="K1" s="10"/>
+      <c r="K1" s="9"/>
       <c r="M1" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="N1" s="10"/>
+      <c r="N1" s="9"/>
       <c r="P1" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="Q1" s="10"/>
+      <c r="Q1" s="9"/>
     </row>
     <row r="2" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
@@ -1069,23 +1086,23 @@
       <c r="A14" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="10"/>
+      <c r="B14" s="9"/>
       <c r="D14" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="E14" s="10"/>
+      <c r="E14" s="9"/>
       <c r="G14" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="H14" s="10"/>
+      <c r="H14" s="9"/>
       <c r="J14" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="K14" s="10"/>
+      <c r="K14" s="9"/>
       <c r="M14" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="N14" s="10"/>
+      <c r="N14" s="9"/>
     </row>
     <row r="15" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
@@ -1374,26 +1391,26 @@
       </c>
     </row>
     <row r="28" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A28" s="9" t="s">
+      <c r="A28" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="B28" s="9"/>
-      <c r="D28" s="9" t="s">
+      <c r="B28" s="10"/>
+      <c r="D28" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="E28" s="9"/>
-      <c r="G28" s="9" t="s">
+      <c r="E28" s="10"/>
+      <c r="G28" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="H28" s="9"/>
+      <c r="H28" s="10"/>
       <c r="J28" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="K28" s="9"/>
+      <c r="K28" s="10"/>
       <c r="M28" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="N28" s="9"/>
+      <c r="N28" s="10"/>
     </row>
     <row r="29" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
@@ -1519,15 +1536,19 @@
       <c r="G34" s="1"/>
       <c r="H34" s="2"/>
     </row>
-    <row r="36" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="B36" s="9"/>
+      <c r="B36" s="10"/>
       <c r="D36" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="E36" s="9"/>
+      <c r="E36" s="10"/>
+      <c r="G36" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="H36" s="9"/>
     </row>
     <row r="37" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
@@ -1542,6 +1563,12 @@
       <c r="E37" s="2" t="s">
         <v>4</v>
       </c>
+      <c r="G37" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H37" s="11" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="38" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
@@ -1555,6 +1582,12 @@
       </c>
       <c r="E38" s="2" t="s">
         <v>6</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H38" s="11" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
@@ -1566,6 +1599,12 @@
       <c r="E39" s="2" t="s">
         <v>8</v>
       </c>
+      <c r="G39" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H39" s="11" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="40" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="D40" s="1" t="s">
@@ -1576,7 +1615,15 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="18">
+  <mergeCells count="19">
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="D36:E36"/>
+    <mergeCell ref="M28:N28"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="G28:H28"/>
+    <mergeCell ref="G36:H36"/>
     <mergeCell ref="M1:N1"/>
     <mergeCell ref="P1:Q1"/>
     <mergeCell ref="D14:E14"/>
@@ -1588,13 +1635,6 @@
     <mergeCell ref="G14:H14"/>
     <mergeCell ref="J14:K14"/>
     <mergeCell ref="M14:N14"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="D36:E36"/>
-    <mergeCell ref="M28:N28"/>
-    <mergeCell ref="A36:B36"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="G28:H28"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Teletrabajo/Teletrabajo.xlsx
+++ b/Teletrabajo/Teletrabajo.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Daniel Puentes\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Luís Fuentes\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A8D5AAD-EBDF-46B5-BE47-BA70C5B65919}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{654ACA85-0696-48F4-A20F-ED4AFD8E7532}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-25905" yWindow="4830" windowWidth="21600" windowHeight="11340" xr2:uid="{DD785F99-1408-4CF3-B821-6417BD60C94A}"/>
+    <workbookView xWindow="2688" yWindow="2688" windowWidth="17280" windowHeight="8880" xr2:uid="{DD785F99-1408-4CF3-B821-6417BD60C94A}"/>
   </bookViews>
   <sheets>
     <sheet name="Teletrabajo" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="46">
   <si>
     <t>Josue</t>
   </si>
@@ -174,6 +174,9 @@
   </si>
   <si>
     <t>Semana del 31 Agosto al 4 de Septiembre</t>
+  </si>
+  <si>
+    <t>Semana del 7 al 11  Septiembre</t>
   </si>
 </sst>
 </file>
@@ -328,16 +331,16 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -673,52 +676,52 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28B5EDDC-5ADB-4A4C-9736-3AC62D35C32F}">
   <dimension ref="A1:Q40"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="18.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="18.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.5546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.42578125" customWidth="1"/>
-    <col min="4" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="5" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="4.85546875" customWidth="1"/>
-    <col min="7" max="7" width="19.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="4.5703125" customWidth="1"/>
-    <col min="11" max="11" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="3.85546875" customWidth="1"/>
-    <col min="14" max="14" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="3.7109375" customWidth="1"/>
-    <col min="17" max="17" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="3.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.44140625" customWidth="1"/>
+    <col min="4" max="4" width="18.6640625" customWidth="1"/>
+    <col min="5" max="5" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.88671875" customWidth="1"/>
+    <col min="7" max="7" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="4.5546875" customWidth="1"/>
+    <col min="11" max="11" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="3.88671875" customWidth="1"/>
+    <col min="14" max="14" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="3.6640625" customWidth="1"/>
+    <col min="17" max="17" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="3.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+    <row r="1" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="D1" s="8" t="s">
+      <c r="B1" s="11"/>
+      <c r="D1" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="E1" s="9"/>
-      <c r="G1" s="8" t="s">
+      <c r="E1" s="11"/>
+      <c r="G1" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="H1" s="9"/>
-      <c r="J1" s="8" t="s">
+      <c r="H1" s="11"/>
+      <c r="J1" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="K1" s="9"/>
-      <c r="M1" s="8" t="s">
+      <c r="K1" s="11"/>
+      <c r="M1" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="N1" s="9"/>
-      <c r="P1" s="8" t="s">
+      <c r="N1" s="11"/>
+      <c r="P1" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="Q1" s="9"/>
-    </row>
-    <row r="2" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q1" s="11"/>
+    </row>
+    <row r="2" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>24</v>
       </c>
@@ -756,7 +759,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>16</v>
       </c>
@@ -794,7 +797,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
@@ -832,7 +835,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>10</v>
       </c>
@@ -870,7 +873,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>13</v>
       </c>
@@ -908,7 +911,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>14</v>
       </c>
@@ -946,7 +949,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>15</v>
       </c>
@@ -984,7 +987,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
       <c r="D9" s="1" t="s">
         <v>5</v>
       </c>
@@ -1016,7 +1019,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
       <c r="G10" s="1" t="s">
         <v>13</v>
       </c>
@@ -1042,7 +1045,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
       <c r="J11" s="1" t="s">
         <v>13</v>
       </c>
@@ -1062,7 +1065,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
       <c r="J12" s="1" t="s">
         <v>14</v>
       </c>
@@ -1082,29 +1085,29 @@
         <v>26</v>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A14" s="8" t="s">
+    <row r="14" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A14" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="9"/>
-      <c r="D14" s="8" t="s">
+      <c r="B14" s="11"/>
+      <c r="D14" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="E14" s="9"/>
-      <c r="G14" s="8" t="s">
+      <c r="E14" s="11"/>
+      <c r="G14" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="H14" s="9"/>
-      <c r="J14" s="8" t="s">
+      <c r="H14" s="11"/>
+      <c r="J14" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="K14" s="9"/>
-      <c r="M14" s="8" t="s">
+      <c r="K14" s="11"/>
+      <c r="M14" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="N14" s="9"/>
-    </row>
-    <row r="15" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="N14" s="11"/>
+    </row>
+    <row r="15" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
         <v>24</v>
       </c>
@@ -1136,7 +1139,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>16</v>
       </c>
@@ -1168,7 +1171,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>15</v>
       </c>
@@ -1200,7 +1203,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>5</v>
       </c>
@@ -1232,7 +1235,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1264,7 +1267,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="20" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>10</v>
       </c>
@@ -1296,7 +1299,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="21" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>12</v>
       </c>
@@ -1328,7 +1331,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="22" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>3</v>
       </c>
@@ -1354,7 +1357,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="23" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>0</v>
       </c>
@@ -1374,7 +1377,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="24" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>13</v>
       </c>
@@ -1382,7 +1385,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="25" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>2</v>
       </c>
@@ -1390,7 +1393,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A28" s="10" t="s">
         <v>34</v>
       </c>
@@ -1403,16 +1406,16 @@
         <v>32</v>
       </c>
       <c r="H28" s="10"/>
-      <c r="J28" s="8" t="s">
+      <c r="J28" s="9" t="s">
         <v>40</v>
       </c>
       <c r="K28" s="10"/>
-      <c r="M28" s="8" t="s">
+      <c r="M28" s="9" t="s">
         <v>41</v>
       </c>
       <c r="N28" s="10"/>
     </row>
-    <row r="29" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A29" s="7" t="s">
         <v>5</v>
       </c>
@@ -1444,7 +1447,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="30" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A30" s="7" t="s">
         <v>3</v>
       </c>
@@ -1476,7 +1479,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="31" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A31" s="7" t="s">
         <v>13</v>
       </c>
@@ -1508,7 +1511,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="32" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A32" s="7" t="s">
         <v>16</v>
       </c>
@@ -1522,7 +1525,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A33" s="7" t="s">
         <v>2</v>
       </c>
@@ -1532,25 +1535,29 @@
       <c r="G33" s="1"/>
       <c r="H33" s="2"/>
     </row>
-    <row r="34" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="G34" s="1"/>
       <c r="H34" s="2"/>
     </row>
-    <row r="36" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="8" t="s">
+    <row r="36" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="9" t="s">
         <v>42</v>
       </c>
       <c r="B36" s="10"/>
-      <c r="D36" s="8" t="s">
+      <c r="D36" s="9" t="s">
         <v>43</v>
       </c>
       <c r="E36" s="10"/>
-      <c r="G36" s="8" t="s">
+      <c r="G36" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="H36" s="9"/>
-    </row>
-    <row r="37" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="H36" s="11"/>
+      <c r="J36" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="K36" s="11"/>
+    </row>
+    <row r="37" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
         <v>2</v>
       </c>
@@ -1566,11 +1573,17 @@
       <c r="G37" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="H37" s="11" t="s">
+      <c r="H37" s="8" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="38" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J37" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="K37" s="8" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
         <v>15</v>
       </c>
@@ -1586,11 +1599,17 @@
       <c r="G38" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="H38" s="11" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="H38" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="J38" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="K38" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A39" s="1"/>
       <c r="B39" s="2"/>
       <c r="D39" s="1" t="s">
@@ -1602,28 +1621,32 @@
       <c r="G39" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="H39" s="11" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="H39" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="J39" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="K39" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="D40" s="1" t="s">
         <v>0</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>11</v>
       </c>
+      <c r="J40" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="K40" s="8" t="s">
+        <v>8</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="19">
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="D36:E36"/>
-    <mergeCell ref="M28:N28"/>
-    <mergeCell ref="A36:B36"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="G28:H28"/>
-    <mergeCell ref="G36:H36"/>
+  <mergeCells count="20">
     <mergeCell ref="M1:N1"/>
     <mergeCell ref="P1:Q1"/>
     <mergeCell ref="D14:E14"/>
@@ -1635,6 +1658,15 @@
     <mergeCell ref="G14:H14"/>
     <mergeCell ref="J14:K14"/>
     <mergeCell ref="M14:N14"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="D36:E36"/>
+    <mergeCell ref="M28:N28"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="G28:H28"/>
+    <mergeCell ref="G36:H36"/>
+    <mergeCell ref="J36:K36"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Teletrabajo/Teletrabajo.xlsx
+++ b/Teletrabajo/Teletrabajo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Luís Fuentes\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{654ACA85-0696-48F4-A20F-ED4AFD8E7532}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22971DFB-54E8-4B77-908B-2C32C410BE52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2688" yWindow="2688" windowWidth="17280" windowHeight="8880" xr2:uid="{DD785F99-1408-4CF3-B821-6417BD60C94A}"/>
+    <workbookView xWindow="1536" yWindow="1536" windowWidth="17280" windowHeight="8880" xr2:uid="{DD785F99-1408-4CF3-B821-6417BD60C94A}"/>
   </bookViews>
   <sheets>
     <sheet name="Teletrabajo" sheetId="1" r:id="rId1"/>
@@ -335,10 +335,10 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -699,27 +699,27 @@
       <c r="A1" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="11"/>
+      <c r="B1" s="10"/>
       <c r="D1" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="E1" s="11"/>
+      <c r="E1" s="10"/>
       <c r="G1" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="H1" s="11"/>
+      <c r="H1" s="10"/>
       <c r="J1" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="K1" s="11"/>
+      <c r="K1" s="10"/>
       <c r="M1" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="N1" s="11"/>
+      <c r="N1" s="10"/>
       <c r="P1" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="Q1" s="11"/>
+      <c r="Q1" s="10"/>
     </row>
     <row r="2" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
@@ -1089,23 +1089,23 @@
       <c r="A14" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="11"/>
+      <c r="B14" s="10"/>
       <c r="D14" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="E14" s="11"/>
+      <c r="E14" s="10"/>
       <c r="G14" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="H14" s="11"/>
+      <c r="H14" s="10"/>
       <c r="J14" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="K14" s="11"/>
+      <c r="K14" s="10"/>
       <c r="M14" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="N14" s="11"/>
+      <c r="N14" s="10"/>
     </row>
     <row r="15" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
@@ -1394,26 +1394,26 @@
       </c>
     </row>
     <row r="28" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A28" s="10" t="s">
+      <c r="A28" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="B28" s="10"/>
-      <c r="D28" s="10" t="s">
+      <c r="B28" s="11"/>
+      <c r="D28" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="E28" s="10"/>
-      <c r="G28" s="10" t="s">
+      <c r="E28" s="11"/>
+      <c r="G28" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="H28" s="10"/>
+      <c r="H28" s="11"/>
       <c r="J28" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="K28" s="10"/>
+      <c r="K28" s="11"/>
       <c r="M28" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="N28" s="10"/>
+      <c r="N28" s="11"/>
     </row>
     <row r="29" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A29" s="7" t="s">
@@ -1543,19 +1543,19 @@
       <c r="A36" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B36" s="10"/>
+      <c r="B36" s="11"/>
       <c r="D36" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="E36" s="10"/>
+      <c r="E36" s="11"/>
       <c r="G36" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="H36" s="11"/>
+      <c r="H36" s="10"/>
       <c r="J36" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="K36" s="11"/>
+      <c r="K36" s="10"/>
     </row>
     <row r="37" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
@@ -1577,7 +1577,7 @@
         <v>1</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K37" s="8" t="s">
         <v>1</v>
@@ -1603,7 +1603,7 @@
         <v>4</v>
       </c>
       <c r="J38" s="1" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K38" s="8" t="s">
         <v>4</v>
@@ -1647,6 +1647,15 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="D36:E36"/>
+    <mergeCell ref="M28:N28"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="G28:H28"/>
+    <mergeCell ref="G36:H36"/>
+    <mergeCell ref="J36:K36"/>
     <mergeCell ref="M1:N1"/>
     <mergeCell ref="P1:Q1"/>
     <mergeCell ref="D14:E14"/>
@@ -1658,15 +1667,6 @@
     <mergeCell ref="G14:H14"/>
     <mergeCell ref="J14:K14"/>
     <mergeCell ref="M14:N14"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="D36:E36"/>
-    <mergeCell ref="M28:N28"/>
-    <mergeCell ref="A36:B36"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="G28:H28"/>
-    <mergeCell ref="G36:H36"/>
-    <mergeCell ref="J36:K36"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Teletrabajo/Teletrabajo.xlsx
+++ b/Teletrabajo/Teletrabajo.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23001"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Luís Fuentes\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Luis Alfredo Fuentes\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22971DFB-54E8-4B77-908B-2C32C410BE52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25B5EA0E-6D2B-4274-A181-379D98C898EE}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1536" yWindow="1536" windowWidth="17280" windowHeight="8880" xr2:uid="{DD785F99-1408-4CF3-B821-6417BD60C94A}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{DD785F99-1408-4CF3-B821-6417BD60C94A}"/>
   </bookViews>
   <sheets>
     <sheet name="Teletrabajo" sheetId="1" r:id="rId1"/>
@@ -26,9 +26,6 @@
         <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
@@ -39,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="47">
   <si>
     <t>Josue</t>
   </si>
@@ -177,13 +174,16 @@
   </si>
   <si>
     <t>Semana del 7 al 11  Septiembre</t>
+  </si>
+  <si>
+    <t>Semana del 14 al 18  Septiembre</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -314,7 +314,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -335,11 +335,17 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -676,52 +682,52 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28B5EDDC-5ADB-4A4C-9736-3AC62D35C32F}">
   <dimension ref="A1:Q40"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="18.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="18.8984375" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.59765625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.44140625" customWidth="1"/>
-    <col min="4" max="4" width="18.6640625" customWidth="1"/>
-    <col min="5" max="5" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="4.88671875" customWidth="1"/>
-    <col min="7" max="7" width="19.5546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="4.5546875" customWidth="1"/>
-    <col min="11" max="11" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="3.88671875" customWidth="1"/>
-    <col min="14" max="14" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="3.6640625" customWidth="1"/>
-    <col min="17" max="17" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="3.6640625" customWidth="1"/>
+    <col min="3" max="3" width="4.3984375" customWidth="1"/>
+    <col min="4" max="4" width="18.69921875" customWidth="1"/>
+    <col min="5" max="5" width="12.296875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.8984375" customWidth="1"/>
+    <col min="7" max="7" width="19.59765625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.69921875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="4.59765625" customWidth="1"/>
+    <col min="11" max="11" width="12.296875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="3.8984375" customWidth="1"/>
+    <col min="14" max="14" width="12.296875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="3.69921875" customWidth="1"/>
+    <col min="17" max="17" width="12.296875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="3.69921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" ht="15.6" customHeight="1">
       <c r="A1" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="10"/>
+      <c r="B1" s="11"/>
       <c r="D1" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="E1" s="10"/>
+      <c r="E1" s="11"/>
       <c r="G1" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="H1" s="10"/>
+      <c r="H1" s="11"/>
       <c r="J1" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="K1" s="10"/>
+      <c r="K1" s="11"/>
       <c r="M1" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="N1" s="10"/>
+      <c r="N1" s="11"/>
       <c r="P1" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="Q1" s="10"/>
-    </row>
-    <row r="2" spans="1:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q1" s="11"/>
+    </row>
+    <row r="2" spans="1:17" ht="15.6" customHeight="1">
       <c r="A2" s="4" t="s">
         <v>24</v>
       </c>
@@ -759,7 +765,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:17" ht="15.6">
       <c r="A3" s="1" t="s">
         <v>16</v>
       </c>
@@ -797,7 +803,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:17" ht="15.6">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
@@ -835,7 +841,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:17" ht="15.6">
       <c r="A5" s="1" t="s">
         <v>10</v>
       </c>
@@ -873,7 +879,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:17" ht="15.6">
       <c r="A6" s="1" t="s">
         <v>13</v>
       </c>
@@ -911,7 +917,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:17" ht="15.6">
       <c r="A7" s="1" t="s">
         <v>14</v>
       </c>
@@ -949,7 +955,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:17" ht="15.6">
       <c r="A8" s="1" t="s">
         <v>15</v>
       </c>
@@ -987,7 +993,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:17" ht="15.6">
       <c r="D9" s="1" t="s">
         <v>5</v>
       </c>
@@ -1019,7 +1025,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:17" ht="15.6">
       <c r="G10" s="1" t="s">
         <v>13</v>
       </c>
@@ -1045,7 +1051,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:17" ht="15.6">
       <c r="J11" s="1" t="s">
         <v>13</v>
       </c>
@@ -1065,7 +1071,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:17" ht="15.6">
       <c r="J12" s="1" t="s">
         <v>14</v>
       </c>
@@ -1085,29 +1091,29 @@
         <v>26</v>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:17" ht="15.6">
       <c r="A14" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="10"/>
+      <c r="B14" s="11"/>
       <c r="D14" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="E14" s="10"/>
+      <c r="E14" s="11"/>
       <c r="G14" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="H14" s="10"/>
+      <c r="H14" s="11"/>
       <c r="J14" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="K14" s="10"/>
+      <c r="K14" s="11"/>
       <c r="M14" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="N14" s="10"/>
-    </row>
-    <row r="15" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="N14" s="11"/>
+    </row>
+    <row r="15" spans="1:17" ht="15.6">
       <c r="A15" s="4" t="s">
         <v>24</v>
       </c>
@@ -1139,7 +1145,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:17" ht="15.6">
       <c r="A16" s="1" t="s">
         <v>16</v>
       </c>
@@ -1171,7 +1177,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:14" ht="15.6">
       <c r="A17" s="1" t="s">
         <v>15</v>
       </c>
@@ -1203,7 +1209,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:14" ht="15.6">
       <c r="A18" s="1" t="s">
         <v>5</v>
       </c>
@@ -1235,7 +1241,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:14" ht="15.6">
       <c r="A19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1267,7 +1273,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="20" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:14" ht="15.6">
       <c r="A20" s="1" t="s">
         <v>10</v>
       </c>
@@ -1299,7 +1305,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="21" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:14" ht="15.6">
       <c r="A21" s="1" t="s">
         <v>12</v>
       </c>
@@ -1331,7 +1337,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="22" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:14" ht="15.6">
       <c r="A22" s="1" t="s">
         <v>3</v>
       </c>
@@ -1357,7 +1363,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="23" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:14" ht="15.6">
       <c r="A23" s="1" t="s">
         <v>0</v>
       </c>
@@ -1377,7 +1383,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="24" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:14" ht="15.6">
       <c r="A24" s="1" t="s">
         <v>13</v>
       </c>
@@ -1385,7 +1391,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="25" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:14" ht="15.6">
       <c r="A25" s="1" t="s">
         <v>2</v>
       </c>
@@ -1393,29 +1399,29 @@
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A28" s="11" t="s">
+    <row r="28" spans="1:14" ht="15.6">
+      <c r="A28" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="B28" s="11"/>
-      <c r="D28" s="11" t="s">
+      <c r="B28" s="10"/>
+      <c r="D28" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="E28" s="11"/>
-      <c r="G28" s="11" t="s">
+      <c r="E28" s="10"/>
+      <c r="G28" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="H28" s="11"/>
+      <c r="H28" s="10"/>
       <c r="J28" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="K28" s="11"/>
+      <c r="K28" s="10"/>
       <c r="M28" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="N28" s="11"/>
-    </row>
-    <row r="29" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="N28" s="10"/>
+    </row>
+    <row r="29" spans="1:14" ht="15.6">
       <c r="A29" s="7" t="s">
         <v>5</v>
       </c>
@@ -1447,7 +1453,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="30" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:14" ht="15.6">
       <c r="A30" s="7" t="s">
         <v>3</v>
       </c>
@@ -1479,7 +1485,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="31" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:14" ht="15.6">
       <c r="A31" s="7" t="s">
         <v>13</v>
       </c>
@@ -1511,7 +1517,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="32" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:14" ht="15.6">
       <c r="A32" s="7" t="s">
         <v>16</v>
       </c>
@@ -1525,7 +1531,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="33" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:14" ht="15.6">
       <c r="A33" s="7" t="s">
         <v>2</v>
       </c>
@@ -1535,29 +1541,33 @@
       <c r="G33" s="1"/>
       <c r="H33" s="2"/>
     </row>
-    <row r="34" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:14" ht="15.6">
       <c r="G34" s="1"/>
       <c r="H34" s="2"/>
     </row>
-    <row r="36" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:14" ht="31.5" customHeight="1">
       <c r="A36" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B36" s="11"/>
+      <c r="B36" s="10"/>
       <c r="D36" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="E36" s="11"/>
+      <c r="E36" s="10"/>
       <c r="G36" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="H36" s="10"/>
+      <c r="H36" s="11"/>
       <c r="J36" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="K36" s="10"/>
-    </row>
-    <row r="37" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="K36" s="11"/>
+      <c r="M36" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="N36" s="13"/>
+    </row>
+    <row r="37" spans="1:14" ht="15.6">
       <c r="A37" s="1" t="s">
         <v>2</v>
       </c>
@@ -1582,8 +1592,14 @@
       <c r="K37" s="8" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="38" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="M37" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="N37" s="8" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" ht="15.6">
       <c r="A38" s="1" t="s">
         <v>15</v>
       </c>
@@ -1608,8 +1624,14 @@
       <c r="K38" s="8" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="39" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="M38" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="N38" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" ht="15.6">
       <c r="A39" s="1"/>
       <c r="B39" s="2"/>
       <c r="D39" s="1" t="s">
@@ -1630,8 +1652,14 @@
       <c r="K39" s="8" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="40" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="M39" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="N39" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" ht="15.6">
       <c r="D40" s="1" t="s">
         <v>0</v>
       </c>
@@ -1644,18 +1672,15 @@
       <c r="K40" s="8" t="s">
         <v>8</v>
       </c>
+      <c r="M40" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="N40" s="8" t="s">
+        <v>11</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="20">
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="D36:E36"/>
-    <mergeCell ref="M28:N28"/>
-    <mergeCell ref="A36:B36"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="G28:H28"/>
-    <mergeCell ref="G36:H36"/>
-    <mergeCell ref="J36:K36"/>
+  <mergeCells count="21">
     <mergeCell ref="M1:N1"/>
     <mergeCell ref="P1:Q1"/>
     <mergeCell ref="D14:E14"/>
@@ -1667,6 +1692,16 @@
     <mergeCell ref="G14:H14"/>
     <mergeCell ref="J14:K14"/>
     <mergeCell ref="M14:N14"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="D36:E36"/>
+    <mergeCell ref="M28:N28"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="G28:H28"/>
+    <mergeCell ref="G36:H36"/>
+    <mergeCell ref="J36:K36"/>
+    <mergeCell ref="M36:N36"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
